--- a/additional_data.xlsx
+++ b/additional_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mooli\Desktop\AI Data project Local\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4190800-620E-4396-8288-01426C6719B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FBEA18-83E2-4813-A341-6FF5AC851278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="11660" windowWidth="14400" windowHeight="7270" xr2:uid="{E38953A6-1F8B-4E58-9729-8D6FEC0256F8}"/>
+    <workbookView xWindow="-40" yWindow="10690" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{E38953A6-1F8B-4E58-9729-8D6FEC0256F8}"/>
   </bookViews>
   <sheets>
     <sheet name="dim_customer" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">dim_card_association!$A$1:$C$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dim_customer!$A$1:$D$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">fact_card_ledger!$A$1:$H$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">fact_credit_bureau!$A$1:$C$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -735,14 +736,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE00A85C-0035-4301-A4BF-00F3238670F5}">
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -759,7 +760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
@@ -776,7 +777,7 @@
         <v>5423121</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>100002</v>
       </c>
@@ -793,7 +794,7 @@
         <v>5423122</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>100003</v>
       </c>
@@ -810,7 +811,7 @@
         <v>5423123</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>100004</v>
       </c>
@@ -827,7 +828,7 @@
         <v>5423124</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>100005</v>
       </c>
@@ -844,7 +845,7 @@
         <v>5423125</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>100006</v>
       </c>
@@ -861,7 +862,7 @@
         <v>5423126</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>100007</v>
       </c>
@@ -878,7 +879,7 @@
         <v>5423127</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>100008</v>
       </c>
@@ -895,7 +896,7 @@
         <v>5423128</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>100009</v>
       </c>
@@ -912,7 +913,7 @@
         <v>5423129</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>100010</v>
       </c>
@@ -929,7 +930,7 @@
         <v>5423130</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>100011</v>
       </c>
@@ -946,7 +947,7 @@
         <v>5423131</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>100012</v>
       </c>
@@ -963,7 +964,7 @@
         <v>5423132</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>100013</v>
       </c>
@@ -980,7 +981,7 @@
         <v>5423133</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>100014</v>
       </c>
@@ -997,7 +998,7 @@
         <v>5423134</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>100015</v>
       </c>
@@ -1014,7 +1015,7 @@
         <v>5423135</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>100016</v>
       </c>
@@ -1031,7 +1032,7 @@
         <v>5423136</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>100017</v>
       </c>
@@ -1048,7 +1049,7 @@
         <v>5423137</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>100018</v>
       </c>
@@ -1065,7 +1066,7 @@
         <v>5423138</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>100019</v>
       </c>
@@ -1082,7 +1083,7 @@
         <v>5423139</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>100020</v>
       </c>
@@ -1099,7 +1100,7 @@
         <v>5423140</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>100021</v>
       </c>
@@ -1116,7 +1117,7 @@
         <v>5423141</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>100022</v>
       </c>
@@ -1133,7 +1134,7 @@
         <v>5423142</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>100023</v>
       </c>
@@ -1150,7 +1151,7 @@
         <v>5423143</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>100024</v>
       </c>
@@ -1167,7 +1168,7 @@
         <v>5423144</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>100025</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>5423145</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>100026</v>
       </c>
@@ -1201,7 +1202,7 @@
         <v>5423146</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>100027</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>5423147</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>100028</v>
       </c>
@@ -1235,7 +1236,7 @@
         <v>5423148</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>100029</v>
       </c>
@@ -1252,7 +1253,7 @@
         <v>5423149</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>100030</v>
       </c>
@@ -1269,7 +1270,7 @@
         <v>5423150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>100031</v>
       </c>
@@ -1286,7 +1287,7 @@
         <v>5423151</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>100032</v>
       </c>
@@ -1303,7 +1304,7 @@
         <v>5423152</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>100033</v>
       </c>
@@ -1320,7 +1321,7 @@
         <v>5423153</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>100034</v>
       </c>
@@ -1337,7 +1338,7 @@
         <v>5423154</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>100035</v>
       </c>
@@ -1354,7 +1355,7 @@
         <v>5423155</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>100036</v>
       </c>
@@ -1371,7 +1372,7 @@
         <v>5423156</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>100037</v>
       </c>
@@ -1388,7 +1389,7 @@
         <v>5423157</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>100038</v>
       </c>
@@ -1405,7 +1406,7 @@
         <v>5423158</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>100039</v>
       </c>
@@ -1422,7 +1423,7 @@
         <v>5423159</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>100040</v>
       </c>
@@ -1439,7 +1440,7 @@
         <v>5423160</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>100041</v>
       </c>
@@ -1456,7 +1457,7 @@
         <v>5423161</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>100042</v>
       </c>
@@ -1473,7 +1474,7 @@
         <v>5423162</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>100043</v>
       </c>
@@ -1490,7 +1491,7 @@
         <v>5423163</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>100044</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>5423164</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>100045</v>
       </c>
@@ -1524,7 +1525,7 @@
         <v>5423165</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>100046</v>
       </c>
@@ -1541,7 +1542,7 @@
         <v>5423166</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>100047</v>
       </c>
@@ -1558,7 +1559,7 @@
         <v>5423167</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>100048</v>
       </c>
@@ -1575,7 +1576,7 @@
         <v>5423168</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>100049</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>5423169</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>100050</v>
       </c>
@@ -1609,7 +1610,7 @@
         <v>5423170</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>100051</v>
       </c>
@@ -1626,7 +1627,7 @@
         <v>5423171</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>100052</v>
       </c>
@@ -1643,7 +1644,7 @@
         <v>5423172</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>100053</v>
       </c>
@@ -1660,7 +1661,7 @@
         <v>5423173</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>100054</v>
       </c>
@@ -1677,7 +1678,7 @@
         <v>5423174</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>100055</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>5423175</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>100056</v>
       </c>
@@ -1711,7 +1712,7 @@
         <v>5423176</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>100057</v>
       </c>
@@ -1728,7 +1729,7 @@
         <v>5423177</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>100058</v>
       </c>
@@ -1745,7 +1746,7 @@
         <v>5423178</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>100059</v>
       </c>
@@ -1762,7 +1763,7 @@
         <v>5423179</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>100060</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>5423180</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>100061</v>
       </c>
@@ -1796,7 +1797,7 @@
         <v>5423181</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>100062</v>
       </c>
@@ -1813,7 +1814,7 @@
         <v>5423182</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>100063</v>
       </c>
@@ -1830,7 +1831,7 @@
         <v>5423183</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>100064</v>
       </c>
@@ -1847,7 +1848,7 @@
         <v>5423184</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>100065</v>
       </c>
@@ -1864,7 +1865,7 @@
         <v>5423185</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>100066</v>
       </c>
@@ -1881,7 +1882,7 @@
         <v>5423186</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>100067</v>
       </c>
@@ -1898,7 +1899,7 @@
         <v>5423187</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>100068</v>
       </c>
@@ -1915,7 +1916,7 @@
         <v>5423188</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>100069</v>
       </c>
@@ -1932,7 +1933,7 @@
         <v>5423189</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>100070</v>
       </c>
@@ -1949,7 +1950,7 @@
         <v>5423190</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>100071</v>
       </c>
@@ -1966,7 +1967,7 @@
         <v>5423191</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>100072</v>
       </c>
@@ -1983,7 +1984,7 @@
         <v>5423192</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>100073</v>
       </c>
@@ -2000,7 +2001,7 @@
         <v>5423193</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>100074</v>
       </c>
@@ -2017,7 +2018,7 @@
         <v>5423194</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>100075</v>
       </c>
@@ -2034,7 +2035,7 @@
         <v>5423195</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>100076</v>
       </c>
@@ -2051,7 +2052,7 @@
         <v>5423196</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>100077</v>
       </c>
@@ -2068,7 +2069,7 @@
         <v>5423197</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>100078</v>
       </c>
@@ -2085,7 +2086,7 @@
         <v>5423198</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>100079</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>5423199</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>100080</v>
       </c>
@@ -2129,13 +2130,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA847E7-CBD6-45C5-AC94-69FB4E417B41}">
   <dimension ref="A1:C81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>511033851</v>
       </c>
@@ -2157,7 +2158,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>593159081</v>
       </c>
@@ -2168,7 +2169,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>513303185</v>
       </c>
@@ -2179,7 +2180,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>573912771</v>
       </c>
@@ -2190,7 +2191,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>517201737</v>
       </c>
@@ -2201,7 +2202,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>525273991</v>
       </c>
@@ -2212,7 +2213,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>525211133</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>513735191</v>
       </c>
@@ -2234,7 +2235,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>642294237</v>
       </c>
@@ -2245,7 +2246,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>532293237</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>508100285</v>
       </c>
@@ -2267,7 +2268,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>531803713</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>521133730</v>
       </c>
@@ -2289,18 +2290,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>583879507</v>
       </c>
       <c r="B15">
-        <v>731</v>
+        <v>531</v>
       </c>
       <c r="C15" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>529587527</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>553383929</v>
       </c>
@@ -2322,7 +2323,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>551172899</v>
       </c>
@@ -2333,18 +2334,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>555512355</v>
       </c>
       <c r="B19">
-        <v>739</v>
+        <v>539</v>
       </c>
       <c r="C19" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>538703173</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>553012283</v>
       </c>
@@ -2366,7 +2367,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>550523335</v>
       </c>
@@ -2377,7 +2378,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>588922038</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>552179823</v>
       </c>
@@ -2399,18 +2400,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>591287033</v>
       </c>
       <c r="B25">
-        <v>725</v>
+        <v>525</v>
       </c>
       <c r="C25" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>590513223</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>539122885</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>511870010</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>538173231</v>
       </c>
@@ -2454,18 +2455,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>531235129</v>
       </c>
       <c r="B30">
-        <v>726</v>
+        <v>526</v>
       </c>
       <c r="C30" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>533772571</v>
       </c>
@@ -2476,7 +2477,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>520351353</v>
       </c>
@@ -2487,18 +2488,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>533011118</v>
       </c>
       <c r="B33">
-        <v>722</v>
+        <v>522</v>
       </c>
       <c r="C33" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>500998597</v>
       </c>
@@ -2509,7 +2510,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>537183838</v>
       </c>
@@ -2520,7 +2521,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>533318152</v>
       </c>
@@ -2531,7 +2532,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>573553220</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>579713311</v>
       </c>
@@ -2553,7 +2554,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>553209191</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>539728311</v>
       </c>
@@ -2575,7 +2576,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>512830290</v>
       </c>
@@ -2586,7 +2587,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>539037035</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>535317935</v>
       </c>
@@ -2608,7 +2609,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>593158950</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>510890193</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>533735923</v>
       </c>
@@ -2641,7 +2642,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>529118775</v>
       </c>
@@ -2652,18 +2653,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>511553539</v>
       </c>
       <c r="B48">
-        <v>740</v>
+        <v>540</v>
       </c>
       <c r="C48" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>517171530</v>
       </c>
@@ -2674,7 +2675,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>530007180</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>533585519</v>
       </c>
@@ -2696,7 +2697,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>533772571</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>597181732</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>512700302</v>
       </c>
@@ -2729,18 +2730,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>505501893</v>
       </c>
       <c r="B55">
-        <v>725</v>
+        <v>525</v>
       </c>
       <c r="C55" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>571355050</v>
       </c>
@@ -2751,7 +2752,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>558033337</v>
       </c>
@@ -2762,18 +2763,18 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>528211933</v>
       </c>
       <c r="B58">
-        <v>720</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>511798919</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>511799073</v>
       </c>
@@ -2795,7 +2796,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>511713323</v>
       </c>
@@ -2806,7 +2807,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>573898115</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>501703753</v>
       </c>
@@ -2828,7 +2829,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>571255885</v>
       </c>
@@ -2839,7 +2840,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>511337351</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>522518757</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>501391119</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>539109873</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>530333373</v>
       </c>
@@ -2894,7 +2895,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>538519155</v>
       </c>
@@ -2905,7 +2906,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>589821917</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>533359153</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>583271315</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>577129778</v>
       </c>
@@ -2949,7 +2950,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>581370891</v>
       </c>
@@ -2960,7 +2961,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>559253811</v>
       </c>
@@ -2971,7 +2972,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>530913113</v>
       </c>
@@ -2982,7 +2983,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>501273101</v>
       </c>
@@ -2993,7 +2994,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>531092755</v>
       </c>
@@ -3004,7 +3005,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>573055332</v>
       </c>
@@ -3015,7 +3016,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>573066332</v>
       </c>
@@ -3027,6 +3028,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C81" xr:uid="{2AA847E7-CBD6-45C5-AC94-69FB4E417B41}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3034,14 +3036,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88260518-02DD-421A-8DD1-AC8718D35564}">
   <dimension ref="A1:C81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3052,7 +3054,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>5423121</v>
       </c>
@@ -3063,7 +3065,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>5423122</v>
       </c>
@@ -3074,7 +3076,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>5423123</v>
       </c>
@@ -3085,7 +3087,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5423124</v>
       </c>
@@ -3096,7 +3098,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5423125</v>
       </c>
@@ -3107,7 +3109,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5423126</v>
       </c>
@@ -3118,7 +3120,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5423127</v>
       </c>
@@ -3129,7 +3131,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5423128</v>
       </c>
@@ -3140,7 +3142,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5423129</v>
       </c>
@@ -3151,7 +3153,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>5423130</v>
       </c>
@@ -3162,7 +3164,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5423131</v>
       </c>
@@ -3173,7 +3175,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>5423132</v>
       </c>
@@ -3184,7 +3186,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>5423133</v>
       </c>
@@ -3195,7 +3197,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5423134</v>
       </c>
@@ -3206,7 +3208,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>5423135</v>
       </c>
@@ -3217,7 +3219,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5423136</v>
       </c>
@@ -3228,7 +3230,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>5423137</v>
       </c>
@@ -3239,7 +3241,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>5423138</v>
       </c>
@@ -3250,7 +3252,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>5423139</v>
       </c>
@@ -3261,7 +3263,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>5423140</v>
       </c>
@@ -3272,7 +3274,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>5423141</v>
       </c>
@@ -3283,7 +3285,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>5423142</v>
       </c>
@@ -3294,7 +3296,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>5423143</v>
       </c>
@@ -3305,7 +3307,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>5423144</v>
       </c>
@@ -3316,7 +3318,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>5423145</v>
       </c>
@@ -3327,7 +3329,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>5423146</v>
       </c>
@@ -3338,7 +3340,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>5423147</v>
       </c>
@@ -3349,7 +3351,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>5423148</v>
       </c>
@@ -3360,7 +3362,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>5423149</v>
       </c>
@@ -3371,7 +3373,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5423150</v>
       </c>
@@ -3382,7 +3384,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5423151</v>
       </c>
@@ -3393,7 +3395,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5423152</v>
       </c>
@@ -3404,7 +3406,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5423153</v>
       </c>
@@ -3415,7 +3417,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5423154</v>
       </c>
@@ -3426,7 +3428,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5423155</v>
       </c>
@@ -3437,7 +3439,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5423156</v>
       </c>
@@ -3448,7 +3450,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5423157</v>
       </c>
@@ -3459,7 +3461,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5423158</v>
       </c>
@@ -3470,7 +3472,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>5423159</v>
       </c>
@@ -3481,7 +3483,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>5423160</v>
       </c>
@@ -3492,7 +3494,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>5423161</v>
       </c>
@@ -3503,7 +3505,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5423162</v>
       </c>
@@ -3514,7 +3516,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5423163</v>
       </c>
@@ -3525,7 +3527,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5423164</v>
       </c>
@@ -3536,7 +3538,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5423165</v>
       </c>
@@ -3547,7 +3549,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5423166</v>
       </c>
@@ -3558,7 +3560,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5423167</v>
       </c>
@@ -3569,7 +3571,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5423168</v>
       </c>
@@ -3580,7 +3582,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5423169</v>
       </c>
@@ -3591,7 +3593,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5423170</v>
       </c>
@@ -3602,7 +3604,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>5423171</v>
       </c>
@@ -3613,7 +3615,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5423172</v>
       </c>
@@ -3624,7 +3626,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>5423173</v>
       </c>
@@ -3635,7 +3637,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>5423174</v>
       </c>
@@ -3646,7 +3648,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>5423175</v>
       </c>
@@ -3657,7 +3659,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>5423176</v>
       </c>
@@ -3668,7 +3670,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>5423177</v>
       </c>
@@ -3679,7 +3681,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>5423178</v>
       </c>
@@ -3690,7 +3692,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>5423179</v>
       </c>
@@ -3701,7 +3703,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>5423180</v>
       </c>
@@ -3712,7 +3714,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>5423181</v>
       </c>
@@ -3723,7 +3725,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>5423182</v>
       </c>
@@ -3734,7 +3736,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>5423183</v>
       </c>
@@ -3745,7 +3747,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>5423184</v>
       </c>
@@ -3756,7 +3758,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>5423185</v>
       </c>
@@ -3767,7 +3769,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>5423186</v>
       </c>
@@ -3778,7 +3780,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>5423187</v>
       </c>
@@ -3789,7 +3791,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>5423188</v>
       </c>
@@ -3800,7 +3802,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>5423189</v>
       </c>
@@ -3811,7 +3813,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>5423190</v>
       </c>
@@ -3822,7 +3824,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>5423191</v>
       </c>
@@ -3833,7 +3835,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>5423192</v>
       </c>
@@ -3844,7 +3846,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>5423193</v>
       </c>
@@ -3855,7 +3857,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>5423194</v>
       </c>
@@ -3866,7 +3868,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>5423195</v>
       </c>
@@ -3877,7 +3879,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>5423196</v>
       </c>
@@ -3888,7 +3890,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>5423197</v>
       </c>
@@ -3899,7 +3901,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>5423198</v>
       </c>
@@ -3910,7 +3912,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>5423199</v>
       </c>
@@ -3921,7 +3923,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>5423200</v>
       </c>
@@ -3943,18 +3945,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2BC2CAA-9843-48F2-AD4E-CB0B8D547122}">
   <dimension ref="A1:H81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3980,7 +3982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>5423121</v>
       </c>
@@ -3991,20 +3993,20 @@
         <v>4884</v>
       </c>
       <c r="D2">
-        <v>10000</v>
+        <v>10885</v>
       </c>
       <c r="E2">
         <v>2558</v>
       </c>
       <c r="G2" s="3">
         <f ca="1">TODAY()-H2</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>5423122</v>
       </c>
@@ -4015,20 +4017,20 @@
         <v>5274</v>
       </c>
       <c r="D3">
-        <v>10000</v>
+        <v>11558</v>
       </c>
       <c r="E3">
         <v>2363</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G8" ca="1" si="0">TODAY()-H3</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>5423123</v>
       </c>
@@ -4039,20 +4041,20 @@
         <v>5081</v>
       </c>
       <c r="D4">
-        <v>10000</v>
+        <v>13314</v>
       </c>
       <c r="E4">
         <v>2459.5</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5423124</v>
       </c>
@@ -4063,20 +4065,20 @@
         <v>4674</v>
       </c>
       <c r="D5">
-        <v>10000</v>
+        <v>8072</v>
       </c>
       <c r="E5">
         <v>2663</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5423125</v>
       </c>
@@ -4087,20 +4089,20 @@
         <v>8759</v>
       </c>
       <c r="D6">
-        <v>10000</v>
+        <v>9480</v>
       </c>
       <c r="E6">
         <v>620.5</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5423126</v>
       </c>
@@ -4111,20 +4113,20 @@
         <v>712</v>
       </c>
       <c r="D7">
-        <v>10000</v>
+        <v>15604</v>
       </c>
       <c r="E7">
         <v>4644</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5423127</v>
       </c>
@@ -4135,20 +4137,20 @@
         <v>564</v>
       </c>
       <c r="D8">
-        <v>10000</v>
+        <v>14544</v>
       </c>
       <c r="E8">
         <v>4718</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2">
         <v>46096</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5423128</v>
       </c>
@@ -4159,7 +4161,7 @@
         <v>5685</v>
       </c>
       <c r="D9">
-        <v>10000</v>
+        <v>16173</v>
       </c>
       <c r="E9">
         <v>2157.5</v>
@@ -4172,7 +4174,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5423129</v>
       </c>
@@ -4183,7 +4185,7 @@
         <v>3632</v>
       </c>
       <c r="D10">
-        <v>10000</v>
+        <v>17512</v>
       </c>
       <c r="E10">
         <v>3184</v>
@@ -4195,7 +4197,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>5423130</v>
       </c>
@@ -4206,7 +4208,7 @@
         <v>5793</v>
       </c>
       <c r="D11">
-        <v>10000</v>
+        <v>9537</v>
       </c>
       <c r="E11">
         <v>2103.5</v>
@@ -4219,7 +4221,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5423131</v>
       </c>
@@ -4230,7 +4232,7 @@
         <v>1759</v>
       </c>
       <c r="D12">
-        <v>10000</v>
+        <v>17953</v>
       </c>
       <c r="E12">
         <v>4120.5</v>
@@ -4243,7 +4245,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>5423132</v>
       </c>
@@ -4254,7 +4256,7 @@
         <v>6030</v>
       </c>
       <c r="D13">
-        <v>10000</v>
+        <v>16594</v>
       </c>
       <c r="E13">
         <v>1985</v>
@@ -4267,7 +4269,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>5423133</v>
       </c>
@@ -4278,7 +4280,7 @@
         <v>6448</v>
       </c>
       <c r="D14">
-        <v>10000</v>
+        <v>13727</v>
       </c>
       <c r="E14">
         <v>1776</v>
@@ -4291,7 +4293,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5423134</v>
       </c>
@@ -4302,7 +4304,7 @@
         <v>3190</v>
       </c>
       <c r="D15">
-        <v>10000</v>
+        <v>11551</v>
       </c>
       <c r="E15">
         <v>3405</v>
@@ -4314,7 +4316,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>5423135</v>
       </c>
@@ -4325,7 +4327,7 @@
         <v>8016</v>
       </c>
       <c r="D16">
-        <v>10000</v>
+        <v>19244</v>
       </c>
       <c r="E16">
         <v>992</v>
@@ -4338,7 +4340,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5423136</v>
       </c>
@@ -4349,7 +4351,7 @@
         <v>5557</v>
       </c>
       <c r="D17">
-        <v>10000</v>
+        <v>16614</v>
       </c>
       <c r="E17">
         <v>2221.5</v>
@@ -4362,7 +4364,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>5423137</v>
       </c>
@@ -4373,7 +4375,7 @@
         <v>4451</v>
       </c>
       <c r="D18">
-        <v>10000</v>
+        <v>10367</v>
       </c>
       <c r="E18">
         <v>2774.5</v>
@@ -4386,7 +4388,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>5423138</v>
       </c>
@@ -4397,7 +4399,7 @@
         <v>4028</v>
       </c>
       <c r="D19">
-        <v>10000</v>
+        <v>16604</v>
       </c>
       <c r="E19">
         <v>2986</v>
@@ -4410,7 +4412,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>5423139</v>
       </c>
@@ -4421,7 +4423,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>10000</v>
+        <v>16281</v>
       </c>
       <c r="E20">
         <v>4950</v>
@@ -4434,7 +4436,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>5423140</v>
       </c>
@@ -4445,7 +4447,7 @@
         <v>5202</v>
       </c>
       <c r="D21">
-        <v>10000</v>
+        <v>15128</v>
       </c>
       <c r="E21">
         <v>2399</v>
@@ -4457,7 +4459,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>5423141</v>
       </c>
@@ -4468,7 +4470,7 @@
         <v>3238</v>
       </c>
       <c r="D22">
-        <v>10000</v>
+        <v>14944</v>
       </c>
       <c r="E22">
         <v>3381</v>
@@ -4481,7 +4483,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>5423142</v>
       </c>
@@ -4492,7 +4494,7 @@
         <v>5146</v>
       </c>
       <c r="D23">
-        <v>10000</v>
+        <v>10949</v>
       </c>
       <c r="E23">
         <v>2427</v>
@@ -4505,7 +4507,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>5423143</v>
       </c>
@@ -4516,7 +4518,7 @@
         <v>7924</v>
       </c>
       <c r="D24">
-        <v>10000</v>
+        <v>18602</v>
       </c>
       <c r="E24">
         <v>1038</v>
@@ -4529,7 +4531,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>5423144</v>
       </c>
@@ -4540,7 +4542,7 @@
         <v>2064</v>
       </c>
       <c r="D25">
-        <v>10000</v>
+        <v>9004</v>
       </c>
       <c r="E25">
         <v>3968</v>
@@ -4553,7 +4555,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>5423145</v>
       </c>
@@ -4564,7 +4566,7 @@
         <v>8245</v>
       </c>
       <c r="D26">
-        <v>10000</v>
+        <v>19954</v>
       </c>
       <c r="E26">
         <v>877.5</v>
@@ -4577,7 +4579,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>5423146</v>
       </c>
@@ -4588,7 +4590,7 @@
         <v>934</v>
       </c>
       <c r="D27">
-        <v>10000</v>
+        <v>19047</v>
       </c>
       <c r="E27">
         <v>4533</v>
@@ -4601,7 +4603,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>5423147</v>
       </c>
@@ -4612,7 +4614,7 @@
         <v>2902</v>
       </c>
       <c r="D28">
-        <v>10000</v>
+        <v>15843</v>
       </c>
       <c r="E28">
         <v>3549</v>
@@ -4625,7 +4627,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>5423148</v>
       </c>
@@ -4636,7 +4638,7 @@
         <v>7562</v>
       </c>
       <c r="D29">
-        <v>10000</v>
+        <v>9618</v>
       </c>
       <c r="E29">
         <v>1219</v>
@@ -4649,7 +4651,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>5423149</v>
       </c>
@@ -4660,7 +4662,7 @@
         <v>6381</v>
       </c>
       <c r="D30">
-        <v>10000</v>
+        <v>9289</v>
       </c>
       <c r="E30">
         <v>1809.5</v>
@@ -4673,7 +4675,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5423150</v>
       </c>
@@ -4684,7 +4686,7 @@
         <v>7893</v>
       </c>
       <c r="D31">
-        <v>10000</v>
+        <v>19367</v>
       </c>
       <c r="E31">
         <v>1053.5</v>
@@ -4697,7 +4699,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5423151</v>
       </c>
@@ -4708,7 +4710,7 @@
         <v>6319</v>
       </c>
       <c r="D32">
-        <v>10000</v>
+        <v>11438</v>
       </c>
       <c r="E32">
         <v>1840.5</v>
@@ -4721,7 +4723,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5423152</v>
       </c>
@@ -4732,7 +4734,7 @@
         <v>5451</v>
       </c>
       <c r="D33">
-        <v>10000</v>
+        <v>19407</v>
       </c>
       <c r="E33">
         <v>2274.5</v>
@@ -4745,7 +4747,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5423153</v>
       </c>
@@ -4756,7 +4758,7 @@
         <v>408</v>
       </c>
       <c r="D34">
-        <v>10000</v>
+        <v>11626</v>
       </c>
       <c r="E34">
         <v>4796</v>
@@ -4769,7 +4771,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5423154</v>
       </c>
@@ -4780,7 +4782,7 @@
         <v>4687</v>
       </c>
       <c r="D35">
-        <v>10000</v>
+        <v>12914</v>
       </c>
       <c r="E35">
         <v>2656.5</v>
@@ -4793,7 +4795,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5423155</v>
       </c>
@@ -4804,7 +4806,7 @@
         <v>6520</v>
       </c>
       <c r="D36">
-        <v>10000</v>
+        <v>19800</v>
       </c>
       <c r="E36">
         <v>1740</v>
@@ -4817,7 +4819,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5423156</v>
       </c>
@@ -4828,7 +4830,7 @@
         <v>3701</v>
       </c>
       <c r="D37">
-        <v>10000</v>
+        <v>17404</v>
       </c>
       <c r="E37">
         <v>3149.5</v>
@@ -4841,7 +4843,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5423157</v>
       </c>
@@ -4852,7 +4854,7 @@
         <v>7968</v>
       </c>
       <c r="D38">
-        <v>10000</v>
+        <v>13851</v>
       </c>
       <c r="E38">
         <v>1016</v>
@@ -4865,7 +4867,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5423158</v>
       </c>
@@ -4876,7 +4878,7 @@
         <v>2228</v>
       </c>
       <c r="D39">
-        <v>10000</v>
+        <v>10358</v>
       </c>
       <c r="E39">
         <v>3886</v>
@@ -4889,7 +4891,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>5423159</v>
       </c>
@@ -4900,7 +4902,7 @@
         <v>686</v>
       </c>
       <c r="D40">
-        <v>10000</v>
+        <v>13900</v>
       </c>
       <c r="E40">
         <v>4657</v>
@@ -4913,7 +4915,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>5423160</v>
       </c>
@@ -4924,7 +4926,7 @@
         <v>6596</v>
       </c>
       <c r="D41">
-        <v>10000</v>
+        <v>11676</v>
       </c>
       <c r="E41">
         <v>1702</v>
@@ -4936,7 +4938,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>5423161</v>
       </c>
@@ -4947,7 +4949,7 @@
         <v>2057</v>
       </c>
       <c r="D42">
-        <v>10000</v>
+        <v>19435</v>
       </c>
       <c r="E42">
         <v>3971.5</v>
@@ -4960,7 +4962,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5423162</v>
       </c>
@@ -4971,7 +4973,7 @@
         <v>7738</v>
       </c>
       <c r="D43">
-        <v>10000</v>
+        <v>15572</v>
       </c>
       <c r="E43">
         <v>1131</v>
@@ -4984,7 +4986,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5423163</v>
       </c>
@@ -4995,7 +4997,7 @@
         <v>7355</v>
       </c>
       <c r="D44">
-        <v>10000</v>
+        <v>9397</v>
       </c>
       <c r="E44">
         <v>1322.5</v>
@@ -5008,7 +5010,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5423164</v>
       </c>
@@ -5019,7 +5021,7 @@
         <v>7322</v>
       </c>
       <c r="D45">
-        <v>10000</v>
+        <v>13882</v>
       </c>
       <c r="E45">
         <v>1339</v>
@@ -5032,7 +5034,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5423165</v>
       </c>
@@ -5043,7 +5045,7 @@
         <v>3186</v>
       </c>
       <c r="D46">
-        <v>10000</v>
+        <v>12227</v>
       </c>
       <c r="E46">
         <v>3407</v>
@@ -5056,7 +5058,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5423166</v>
       </c>
@@ -5067,7 +5069,7 @@
         <v>5086</v>
       </c>
       <c r="D47">
-        <v>10000</v>
+        <v>15395</v>
       </c>
       <c r="E47">
         <v>2457</v>
@@ -5080,7 +5082,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5423167</v>
       </c>
@@ -5091,7 +5093,7 @@
         <v>3967</v>
       </c>
       <c r="D48">
-        <v>10000</v>
+        <v>19495</v>
       </c>
       <c r="E48">
         <v>3016.5</v>
@@ -5104,7 +5106,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5423168</v>
       </c>
@@ -5115,20 +5117,20 @@
         <v>8939</v>
       </c>
       <c r="D49">
-        <v>10000</v>
+        <v>8244</v>
       </c>
       <c r="E49">
         <v>530.5</v>
       </c>
       <c r="G49" s="3">
         <f t="shared" ref="G49" ca="1" si="2">TODAY()-H49</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H49" s="2">
         <v>46091</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5423169</v>
       </c>
@@ -5139,7 +5141,7 @@
         <v>5875</v>
       </c>
       <c r="D50">
-        <v>10000</v>
+        <v>10339</v>
       </c>
       <c r="E50">
         <v>2062.5</v>
@@ -5152,7 +5154,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5423170</v>
       </c>
@@ -5163,7 +5165,7 @@
         <v>3619</v>
       </c>
       <c r="D51">
-        <v>10000</v>
+        <v>17383</v>
       </c>
       <c r="E51">
         <v>3190.5</v>
@@ -5176,7 +5178,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>5423171</v>
       </c>
@@ -5187,7 +5189,7 @@
         <v>2792</v>
       </c>
       <c r="D52">
-        <v>10000</v>
+        <v>11642</v>
       </c>
       <c r="E52">
         <v>3604</v>
@@ -5200,7 +5202,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5423172</v>
       </c>
@@ -5211,20 +5213,20 @@
         <v>6690</v>
       </c>
       <c r="D53">
-        <v>10000</v>
+        <v>16502</v>
       </c>
       <c r="E53">
         <v>1655</v>
       </c>
       <c r="G53" s="3">
         <f t="shared" ref="G53" ca="1" si="3">TODAY()-H53</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H53" s="2">
         <v>46091</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>5423173</v>
       </c>
@@ -5235,7 +5237,7 @@
         <v>6880</v>
       </c>
       <c r="D54">
-        <v>10000</v>
+        <v>16880</v>
       </c>
       <c r="E54">
         <v>1560</v>
@@ -5248,7 +5250,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>5423174</v>
       </c>
@@ -5259,7 +5261,7 @@
         <v>2548</v>
       </c>
       <c r="D55">
-        <v>10000</v>
+        <v>8823</v>
       </c>
       <c r="E55">
         <v>3726</v>
@@ -5272,7 +5274,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>5423175</v>
       </c>
@@ -5283,7 +5285,7 @@
         <v>5521</v>
       </c>
       <c r="D56">
-        <v>10000</v>
+        <v>18442</v>
       </c>
       <c r="E56">
         <v>2239.5</v>
@@ -5296,7 +5298,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>5423176</v>
       </c>
@@ -5307,20 +5309,20 @@
         <v>3849</v>
       </c>
       <c r="D57">
-        <v>10000</v>
+        <v>13614</v>
       </c>
       <c r="E57">
         <v>3075.5</v>
       </c>
       <c r="G57" s="3">
         <f t="shared" ref="G57" ca="1" si="4">TODAY()-H57</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H57" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>5423177</v>
       </c>
@@ -5331,7 +5333,7 @@
         <v>1379</v>
       </c>
       <c r="D58">
-        <v>10000</v>
+        <v>12754</v>
       </c>
       <c r="E58">
         <v>4310.5</v>
@@ -5344,7 +5346,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>5423178</v>
       </c>
@@ -5355,7 +5357,7 @@
         <v>4004</v>
       </c>
       <c r="D59">
-        <v>10000</v>
+        <v>12966</v>
       </c>
       <c r="E59">
         <v>2998</v>
@@ -5368,7 +5370,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>5423179</v>
       </c>
@@ -5379,7 +5381,7 @@
         <v>7042</v>
       </c>
       <c r="D60">
-        <v>10000</v>
+        <v>9942</v>
       </c>
       <c r="E60">
         <v>1479</v>
@@ -5392,7 +5394,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>5423180</v>
       </c>
@@ -5403,20 +5405,20 @@
         <v>2058</v>
       </c>
       <c r="D61">
-        <v>10000</v>
+        <v>9029</v>
       </c>
       <c r="E61">
         <v>3971</v>
       </c>
       <c r="G61" s="3">
         <f t="shared" ref="G61" ca="1" si="5">TODAY()-H61</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H61" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>5423181</v>
       </c>
@@ -5427,7 +5429,7 @@
         <v>3807</v>
       </c>
       <c r="D62">
-        <v>10000</v>
+        <v>8896</v>
       </c>
       <c r="E62">
         <v>3096.5</v>
@@ -5440,7 +5442,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>5423182</v>
       </c>
@@ -5451,7 +5453,7 @@
         <v>502</v>
       </c>
       <c r="D63">
-        <v>10000</v>
+        <v>15827</v>
       </c>
       <c r="E63">
         <v>4749</v>
@@ -5464,7 +5466,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>5423183</v>
       </c>
@@ -5475,20 +5477,20 @@
         <v>7764</v>
       </c>
       <c r="D64">
-        <v>10000</v>
+        <v>17916</v>
       </c>
       <c r="E64">
         <v>1118</v>
       </c>
       <c r="G64" s="3">
         <f t="shared" ref="G64" ca="1" si="6">TODAY()-H64</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H64" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>5423184</v>
       </c>
@@ -5499,7 +5501,7 @@
         <v>8019</v>
       </c>
       <c r="D65">
-        <v>10000</v>
+        <v>8874</v>
       </c>
       <c r="E65">
         <v>990.5</v>
@@ -5512,7 +5514,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>5423185</v>
       </c>
@@ -5523,7 +5525,7 @@
         <v>4257</v>
       </c>
       <c r="D66">
-        <v>10000</v>
+        <v>10253</v>
       </c>
       <c r="E66">
         <v>2871.5</v>
@@ -5536,7 +5538,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>5423186</v>
       </c>
@@ -5547,20 +5549,20 @@
         <v>4347</v>
       </c>
       <c r="D67">
-        <v>10000</v>
+        <v>8074</v>
       </c>
       <c r="E67">
         <v>2826.5</v>
       </c>
       <c r="G67" s="3">
         <f t="shared" ref="G67:G81" ca="1" si="7">TODAY()-H67</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H67" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>5423187</v>
       </c>
@@ -5571,7 +5573,7 @@
         <v>7584</v>
       </c>
       <c r="D68">
-        <v>10000</v>
+        <v>8899</v>
       </c>
       <c r="E68">
         <v>1208</v>
@@ -5584,7 +5586,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>5423188</v>
       </c>
@@ -5595,7 +5597,7 @@
         <v>463</v>
       </c>
       <c r="D69">
-        <v>10000</v>
+        <v>12606</v>
       </c>
       <c r="E69">
         <v>4768.5</v>
@@ -5608,7 +5610,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>5423189</v>
       </c>
@@ -5619,7 +5621,7 @@
         <v>1513</v>
       </c>
       <c r="D70">
-        <v>10000</v>
+        <v>18666</v>
       </c>
       <c r="E70">
         <v>4243.5</v>
@@ -5632,7 +5634,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>5423190</v>
       </c>
@@ -5643,7 +5645,7 @@
         <v>2864</v>
       </c>
       <c r="D71">
-        <v>10000</v>
+        <v>13362</v>
       </c>
       <c r="E71">
         <v>3568</v>
@@ -5656,7 +5658,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>5423191</v>
       </c>
@@ -5667,7 +5669,7 @@
         <v>7745</v>
       </c>
       <c r="D72">
-        <v>10000</v>
+        <v>10314</v>
       </c>
       <c r="E72">
         <v>1127.5</v>
@@ -5680,7 +5682,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>5423192</v>
       </c>
@@ -5691,7 +5693,7 @@
         <v>827</v>
       </c>
       <c r="D73">
-        <v>10000</v>
+        <v>16467</v>
       </c>
       <c r="E73">
         <v>4586.5</v>
@@ -5703,7 +5705,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>5423193</v>
       </c>
@@ -5714,20 +5716,20 @@
         <v>43</v>
       </c>
       <c r="D74">
-        <v>10000</v>
+        <v>17073</v>
       </c>
       <c r="E74">
         <v>4978.5</v>
       </c>
       <c r="G74" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H74" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>5423194</v>
       </c>
@@ -5738,20 +5740,20 @@
         <v>2585</v>
       </c>
       <c r="D75">
-        <v>10000</v>
+        <v>8256</v>
       </c>
       <c r="E75">
         <v>3707.5</v>
       </c>
       <c r="G75" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H75" s="2">
         <v>46112</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>5423195</v>
       </c>
@@ -5762,20 +5764,20 @@
         <v>304</v>
       </c>
       <c r="D76">
-        <v>10000</v>
+        <v>17795</v>
       </c>
       <c r="E76">
         <v>4848</v>
       </c>
       <c r="G76" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H76" s="2">
         <v>46099</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>5423196</v>
       </c>
@@ -5786,20 +5788,20 @@
         <v>7333</v>
       </c>
       <c r="D77">
-        <v>10000</v>
+        <v>16614</v>
       </c>
       <c r="E77">
         <v>1333.5</v>
       </c>
       <c r="G77" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H77" s="2">
         <v>46112</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>5423197</v>
       </c>
@@ -5810,20 +5812,20 @@
         <v>798</v>
       </c>
       <c r="D78">
-        <v>10000</v>
+        <v>17054</v>
       </c>
       <c r="E78">
         <v>4601</v>
       </c>
       <c r="G78" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H78" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>5423198</v>
       </c>
@@ -5834,20 +5836,20 @@
         <v>5358</v>
       </c>
       <c r="D79">
-        <v>10000</v>
+        <v>16015</v>
       </c>
       <c r="E79">
         <v>2321</v>
       </c>
       <c r="G79" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H79" s="2">
         <v>46112</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>5423199</v>
       </c>
@@ -5858,20 +5860,20 @@
         <v>3466</v>
       </c>
       <c r="D80">
-        <v>10000</v>
+        <v>15941</v>
       </c>
       <c r="E80">
         <v>3267</v>
       </c>
       <c r="G80" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H80" s="2">
         <v>46082</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>5423200</v>
       </c>
@@ -5882,14 +5884,14 @@
         <v>8207</v>
       </c>
       <c r="D81">
-        <v>10000</v>
+        <v>19833</v>
       </c>
       <c r="E81">
         <v>896.5</v>
       </c>
       <c r="G81" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H81" s="2">
         <v>46082</v>
